--- a/AC_2009/AC_030.xlsx
+++ b/AC_2009/AC_030.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,14 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +65,26 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -82,11 +106,53 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -102,6 +168,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -468,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S249"/>
+  <dimension ref="A1:S251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -513,6 +594,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -15444,73 +15526,213 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C249" s="7">
+      <c r="A249" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL EVM VOTES</t>
+        </is>
+      </c>
+      <c r="B249" s="9" t="inlineStr"/>
+      <c r="C249" s="10">
         <f>SUM(C6:C248)</f>
         <v/>
       </c>
-      <c r="D249" s="7">
+      <c r="D249" s="10">
         <f>SUM(D6:D248)</f>
         <v/>
       </c>
-      <c r="E249" s="7">
+      <c r="E249" s="10">
         <f>SUM(E6:E248)</f>
         <v/>
       </c>
-      <c r="F249" s="7">
+      <c r="F249" s="10">
         <f>SUM(F6:F248)</f>
         <v/>
       </c>
-      <c r="G249" s="7">
+      <c r="G249" s="10">
         <f>SUM(G6:G248)</f>
         <v/>
       </c>
-      <c r="H249" s="7">
+      <c r="H249" s="10">
         <f>SUM(H6:H248)</f>
         <v/>
       </c>
-      <c r="I249" s="7">
+      <c r="I249" s="10">
         <f>SUM(I6:I248)</f>
         <v/>
       </c>
-      <c r="J249" s="7">
+      <c r="J249" s="10">
         <f>SUM(J6:J248)</f>
         <v/>
       </c>
-      <c r="K249" s="7">
+      <c r="K249" s="10">
         <f>SUM(K6:K248)</f>
         <v/>
       </c>
-      <c r="L249" s="7">
+      <c r="L249" s="10">
         <f>SUM(L6:L248)</f>
         <v/>
       </c>
-      <c r="M249" s="7">
+      <c r="M249" s="10">
         <f>SUM(M6:M248)</f>
         <v/>
       </c>
-      <c r="N249" s="7">
+      <c r="N249" s="10">
         <f>SUM(N6:N248)</f>
         <v/>
       </c>
-      <c r="O249" s="7">
+      <c r="O249" s="10">
         <f>SUM(O6:O248)</f>
         <v/>
       </c>
-      <c r="P249" s="7">
+      <c r="P249" s="10">
         <f>SUM(P6:P248)</f>
         <v/>
       </c>
-      <c r="Q249" s="7">
+      <c r="Q249" s="10">
         <f>SUM(Q6:Q248)</f>
         <v/>
       </c>
-      <c r="R249" s="7">
+      <c r="R249" s="10">
         <f>SUM(R6:R248)</f>
+        <v/>
+      </c>
+      <c r="S249" s="10">
+        <f>SUM(S6:S248)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="11" t="inlineStr">
+        <is>
+          <t>POSTAL BALLOT VOTES</t>
+        </is>
+      </c>
+      <c r="B250" s="12" t="inlineStr"/>
+      <c r="C250" s="13" t="n">
+        <v>214</v>
+      </c>
+      <c r="D250" s="13" t="n">
+        <v>197</v>
+      </c>
+      <c r="E250" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="F250" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G250" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H250" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I250" s="13" t="n">
+        <v>173</v>
+      </c>
+      <c r="J250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N250" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O250" s="13" t="n">
+        <v>601</v>
+      </c>
+      <c r="P250" s="13" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q250" s="13" t="n">
+        <v>711</v>
+      </c>
+      <c r="R250" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S250" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="14" t="inlineStr">
+        <is>
+          <t>TOTAL VOTES POLLED</t>
+        </is>
+      </c>
+      <c r="B251" s="15" t="inlineStr"/>
+      <c r="C251" s="16">
+        <f>C249+C250</f>
+        <v/>
+      </c>
+      <c r="D251" s="16">
+        <f>D249+D250</f>
+        <v/>
+      </c>
+      <c r="E251" s="16">
+        <f>E249+E250</f>
+        <v/>
+      </c>
+      <c r="F251" s="16">
+        <f>F249+F250</f>
+        <v/>
+      </c>
+      <c r="G251" s="16">
+        <f>G249+G250</f>
+        <v/>
+      </c>
+      <c r="H251" s="16">
+        <f>H249+H250</f>
+        <v/>
+      </c>
+      <c r="I251" s="16">
+        <f>I249+I250</f>
+        <v/>
+      </c>
+      <c r="J251" s="16">
+        <f>J249+J250</f>
+        <v/>
+      </c>
+      <c r="K251" s="16">
+        <f>K249+K250</f>
+        <v/>
+      </c>
+      <c r="L251" s="16">
+        <f>L249+L250</f>
+        <v/>
+      </c>
+      <c r="M251" s="16">
+        <f>M249+M250</f>
+        <v/>
+      </c>
+      <c r="N251" s="16">
+        <f>N249+N250</f>
+        <v/>
+      </c>
+      <c r="O251" s="16">
+        <f>O249+O250</f>
+        <v/>
+      </c>
+      <c r="P251" s="16">
+        <f>P249+P250</f>
+        <v/>
+      </c>
+      <c r="Q251" s="16">
+        <f>Q249+Q250</f>
+        <v/>
+      </c>
+      <c r="R251" s="16">
+        <f>R249+R250</f>
+        <v/>
+      </c>
+      <c r="S251" s="16">
+        <f>S249+S250</f>
         <v/>
       </c>
     </row>

--- a/AC_2009/AC_030.xlsx
+++ b/AC_2009/AC_030.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -84,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -148,11 +153,19 @@
         <color rgb="001B365D"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -182,6 +195,23 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -594,7 +624,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -15526,212 +15555,212 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="8" t="inlineStr">
+      <c r="A249" s="17" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B249" s="9" t="inlineStr"/>
-      <c r="C249" s="10">
+      <c r="B249" s="18" t="inlineStr"/>
+      <c r="C249" s="19">
         <f>SUM(C6:C248)</f>
         <v/>
       </c>
-      <c r="D249" s="10">
+      <c r="D249" s="19">
         <f>SUM(D6:D248)</f>
         <v/>
       </c>
-      <c r="E249" s="10">
+      <c r="E249" s="19">
         <f>SUM(E6:E248)</f>
         <v/>
       </c>
-      <c r="F249" s="10">
+      <c r="F249" s="19">
         <f>SUM(F6:F248)</f>
         <v/>
       </c>
-      <c r="G249" s="10">
+      <c r="G249" s="19">
         <f>SUM(G6:G248)</f>
         <v/>
       </c>
-      <c r="H249" s="10">
+      <c r="H249" s="19">
         <f>SUM(H6:H248)</f>
         <v/>
       </c>
-      <c r="I249" s="10">
+      <c r="I249" s="19">
         <f>SUM(I6:I248)</f>
         <v/>
       </c>
-      <c r="J249" s="10">
+      <c r="J249" s="19">
         <f>SUM(J6:J248)</f>
         <v/>
       </c>
-      <c r="K249" s="10">
+      <c r="K249" s="19">
         <f>SUM(K6:K248)</f>
         <v/>
       </c>
-      <c r="L249" s="10">
+      <c r="L249" s="19">
         <f>SUM(L6:L248)</f>
         <v/>
       </c>
-      <c r="M249" s="10">
+      <c r="M249" s="19">
         <f>SUM(M6:M248)</f>
         <v/>
       </c>
-      <c r="N249" s="10">
+      <c r="N249" s="19">
         <f>SUM(N6:N248)</f>
         <v/>
       </c>
-      <c r="O249" s="10">
+      <c r="O249" s="19">
         <f>SUM(O6:O248)</f>
         <v/>
       </c>
-      <c r="P249" s="10">
+      <c r="P249" s="19">
         <f>SUM(P6:P248)</f>
         <v/>
       </c>
-      <c r="Q249" s="10">
+      <c r="Q249" s="19">
         <f>SUM(Q6:Q248)</f>
         <v/>
       </c>
-      <c r="R249" s="10">
+      <c r="R249" s="19">
         <f>SUM(R6:R248)</f>
         <v/>
       </c>
-      <c r="S249" s="10">
+      <c r="S249" s="19">
         <f>SUM(S6:S248)</f>
         <v/>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="11" t="inlineStr">
+      <c r="A250" s="20" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
       <c r="B250" s="12" t="inlineStr"/>
-      <c r="C250" s="13" t="n">
+      <c r="C250" s="19" t="n">
         <v>214</v>
       </c>
-      <c r="D250" s="13" t="n">
+      <c r="D250" s="19" t="n">
         <v>197</v>
       </c>
-      <c r="E250" s="13" t="n">
+      <c r="E250" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="F250" s="13" t="n">
+      <c r="F250" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="G250" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H250" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="I250" s="13" t="n">
+      <c r="G250" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H250" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I250" s="19" t="n">
         <v>173</v>
       </c>
-      <c r="J250" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K250" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L250" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M250" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N250" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O250" s="13" t="n">
+      <c r="J250" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K250" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L250" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M250" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N250" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="O250" s="19" t="n">
         <v>601</v>
       </c>
-      <c r="P250" s="13" t="n">
+      <c r="P250" s="19" t="n">
         <v>110</v>
       </c>
-      <c r="Q250" s="13" t="n">
+      <c r="Q250" s="19" t="n">
         <v>711</v>
       </c>
-      <c r="R250" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S250" s="13" t="n">
+      <c r="R250" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S250" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="14" t="inlineStr">
+      <c r="A251" s="21" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B251" s="15" t="inlineStr"/>
-      <c r="C251" s="16">
+      <c r="B251" s="22" t="inlineStr"/>
+      <c r="C251" s="23">
         <f>C249+C250</f>
         <v/>
       </c>
-      <c r="D251" s="16">
+      <c r="D251" s="23">
         <f>D249+D250</f>
         <v/>
       </c>
-      <c r="E251" s="16">
+      <c r="E251" s="23">
         <f>E249+E250</f>
         <v/>
       </c>
-      <c r="F251" s="16">
+      <c r="F251" s="23">
         <f>F249+F250</f>
         <v/>
       </c>
-      <c r="G251" s="16">
+      <c r="G251" s="23">
         <f>G249+G250</f>
         <v/>
       </c>
-      <c r="H251" s="16">
+      <c r="H251" s="23">
         <f>H249+H250</f>
         <v/>
       </c>
-      <c r="I251" s="16">
+      <c r="I251" s="23">
         <f>I249+I250</f>
         <v/>
       </c>
-      <c r="J251" s="16">
+      <c r="J251" s="23">
         <f>J249+J250</f>
         <v/>
       </c>
-      <c r="K251" s="16">
+      <c r="K251" s="23">
         <f>K249+K250</f>
         <v/>
       </c>
-      <c r="L251" s="16">
+      <c r="L251" s="23">
         <f>L249+L250</f>
         <v/>
       </c>
-      <c r="M251" s="16">
+      <c r="M251" s="23">
         <f>M249+M250</f>
         <v/>
       </c>
-      <c r="N251" s="16">
+      <c r="N251" s="23">
         <f>N249+N250</f>
         <v/>
       </c>
-      <c r="O251" s="16">
+      <c r="O251" s="23">
         <f>O249+O250</f>
         <v/>
       </c>
-      <c r="P251" s="16">
+      <c r="P251" s="23">
         <f>P249+P250</f>
         <v/>
       </c>
-      <c r="Q251" s="16">
+      <c r="Q251" s="23">
         <f>Q249+Q250</f>
         <v/>
       </c>
-      <c r="R251" s="16">
+      <c r="R251" s="23">
         <f>R249+R250</f>
         <v/>
       </c>
-      <c r="S251" s="16">
+      <c r="S251" s="23">
         <f>S249+S250</f>
         <v/>
       </c>

--- a/AC_2009/AC_030.xlsx
+++ b/AC_2009/AC_030.xlsx
@@ -1459,7 +1459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S251"/>
+  <dimension ref="A1:R251"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
     <col width="35" customWidth="1" style="1" min="1" max="2"/>
@@ -1478,8 +1478,7 @@
     <col width="17" customWidth="1" style="1" min="16" max="16"/>
     <col width="16" customWidth="1" style="1" min="17" max="17"/>
     <col width="17" customWidth="1" style="1" min="18" max="18"/>
-    <col width="16" customWidth="1" style="1" min="19" max="19"/>
-    <col width="8.851559999999999" customWidth="1" style="1" min="20" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="1" min="19" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.35" customHeight="1" s="24">
@@ -1505,7 +1504,6 @@
       <c r="P1" s="3" t="n"/>
       <c r="Q1" s="3" t="n"/>
       <c r="R1" s="3" t="n"/>
-      <c r="S1" s="3" t="n"/>
     </row>
     <row r="2" ht="13.75" customHeight="1" s="24">
       <c r="A2" s="4" t="inlineStr">
@@ -1530,7 +1528,6 @@
       <c r="P2" s="3" t="n"/>
       <c r="Q2" s="3" t="n"/>
       <c r="R2" s="3" t="n"/>
-      <c r="S2" s="3" t="n"/>
     </row>
     <row r="3" ht="13.75" customHeight="1" s="24">
       <c r="A3" s="4" t="inlineStr">
@@ -1555,7 +1552,6 @@
       <c r="P3" s="3" t="n"/>
       <c r="Q3" s="3" t="n"/>
       <c r="R3" s="3" t="n"/>
-      <c r="S3" s="3" t="n"/>
     </row>
     <row r="4" ht="13.55" customHeight="1" s="24">
       <c r="A4" s="5" t="n"/>
@@ -1576,7 +1572,6 @@
       <c r="P4" s="5" t="n"/>
       <c r="Q4" s="5" t="n"/>
       <c r="R4" s="5" t="n"/>
-      <c r="S4" s="5" t="n"/>
     </row>
     <row r="5" ht="13.55" customHeight="1" s="24">
       <c r="A5" s="6" t="inlineStr">
@@ -1661,17 +1656,12 @@
       </c>
       <c r="Q5" s="7" t="inlineStr">
         <is>
-          <t>Total 17</t>
-        </is>
-      </c>
-      <c r="R5" s="7" t="inlineStr">
+          <t>Total_Votes</t>
+        </is>
+      </c>
+      <c r="R5" s="8" t="inlineStr">
         <is>
           <t>Tendered_Votes</t>
-        </is>
-      </c>
-      <c r="S5" s="8" t="inlineStr">
-        <is>
-          <t>Checksum_Diff</t>
         </is>
       </c>
     </row>
@@ -1732,9 +1722,6 @@
       <c r="R6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S6" s="9" t="n">
-        <v>601</v>
-      </c>
     </row>
     <row r="7" ht="13.55" customHeight="1" s="24">
       <c r="A7" s="9" t="n">
@@ -1793,9 +1780,6 @@
       <c r="R7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S7" s="9" t="n">
-        <v>534</v>
-      </c>
     </row>
     <row r="8" ht="13.55" customHeight="1" s="24">
       <c r="A8" s="9" t="n">
@@ -1854,9 +1838,6 @@
       <c r="R8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S8" s="9" t="n">
-        <v>512</v>
-      </c>
     </row>
     <row r="9" ht="13.55" customHeight="1" s="24">
       <c r="A9" s="9" t="n">
@@ -1915,9 +1896,6 @@
       <c r="R9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" s="9" t="n">
-        <v>319</v>
-      </c>
     </row>
     <row r="10" ht="13.55" customHeight="1" s="24">
       <c r="A10" s="9" t="n">
@@ -1976,9 +1954,6 @@
       <c r="R10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S10" s="9" t="n">
-        <v>439</v>
-      </c>
     </row>
     <row r="11" ht="13.55" customHeight="1" s="24">
       <c r="A11" s="9" t="n">
@@ -2036,9 +2011,6 @@
       </c>
       <c r="R11" s="9" t="n">
         <v>0</v>
-      </c>
-      <c r="S11" s="9" t="n">
-        <v>482</v>
       </c>
     </row>
     <row r="12" ht="13.55" customHeight="1" s="24">
@@ -2098,9 +2070,6 @@
       <c r="R12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S12" s="9" t="n">
-        <v>469</v>
-      </c>
     </row>
     <row r="13" ht="13.55" customHeight="1" s="24">
       <c r="A13" s="9" t="n">
@@ -2159,9 +2128,6 @@
       <c r="R13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S13" s="9" t="n">
-        <v>421</v>
-      </c>
     </row>
     <row r="14" ht="13.55" customHeight="1" s="24">
       <c r="A14" s="9" t="n">
@@ -2220,9 +2186,6 @@
       <c r="R14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S14" s="9" t="n">
-        <v>661</v>
-      </c>
     </row>
     <row r="15" ht="13.55" customHeight="1" s="24">
       <c r="A15" s="9" t="n">
@@ -2281,9 +2244,6 @@
       <c r="R15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S15" s="9" t="n">
-        <v>448</v>
-      </c>
     </row>
     <row r="16" ht="13.55" customHeight="1" s="24">
       <c r="A16" s="9" t="n">
@@ -2342,9 +2302,6 @@
       <c r="R16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S16" s="9" t="n">
-        <v>417</v>
-      </c>
     </row>
     <row r="17" ht="13.55" customHeight="1" s="24">
       <c r="A17" s="9" t="n">
@@ -2403,9 +2360,6 @@
       <c r="R17" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="S17" s="9" t="n">
-        <v>884</v>
-      </c>
     </row>
     <row r="18" ht="13.55" customHeight="1" s="24">
       <c r="A18" s="9" t="n">
@@ -2464,9 +2418,6 @@
       <c r="R18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S18" s="9" t="n">
-        <v>661</v>
-      </c>
     </row>
     <row r="19" ht="13.55" customHeight="1" s="24">
       <c r="A19" s="9" t="n">
@@ -2525,9 +2476,6 @@
       <c r="R19" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S19" s="9" t="n">
-        <v>712</v>
-      </c>
     </row>
     <row r="20" ht="13.55" customHeight="1" s="24">
       <c r="A20" s="9" t="n">
@@ -2586,9 +2534,6 @@
       <c r="R20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S20" s="9" t="n">
-        <v>674</v>
-      </c>
     </row>
     <row r="21" ht="13.55" customHeight="1" s="24">
       <c r="A21" s="9" t="n">
@@ -2647,9 +2592,6 @@
       <c r="R21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S21" s="9" t="n">
-        <v>698</v>
-      </c>
     </row>
     <row r="22" ht="13.55" customHeight="1" s="24">
       <c r="A22" s="9" t="n">
@@ -2708,9 +2650,6 @@
       <c r="R22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S22" s="9" t="n">
-        <v>596</v>
-      </c>
     </row>
     <row r="23" ht="13.55" customHeight="1" s="24">
       <c r="A23" s="9" t="n">
@@ -2769,9 +2708,6 @@
       <c r="R23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S23" s="9" t="n">
-        <v>352</v>
-      </c>
     </row>
     <row r="24" ht="13.55" customHeight="1" s="24">
       <c r="A24" s="9" t="n">
@@ -2830,9 +2766,6 @@
       <c r="R24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S24" s="9" t="n">
-        <v>886</v>
-      </c>
     </row>
     <row r="25" ht="13.55" customHeight="1" s="24">
       <c r="A25" s="9" t="n">
@@ -2891,9 +2824,6 @@
       <c r="R25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S25" s="9" t="n">
-        <v>807</v>
-      </c>
     </row>
     <row r="26" ht="13.55" customHeight="1" s="24">
       <c r="A26" s="9" t="n">
@@ -2952,9 +2882,6 @@
       <c r="R26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S26" s="9" t="n">
-        <v>861</v>
-      </c>
     </row>
     <row r="27" ht="13.55" customHeight="1" s="24">
       <c r="A27" s="9" t="n">
@@ -3013,9 +2940,6 @@
       <c r="R27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S27" s="9" t="n">
-        <v>555</v>
-      </c>
     </row>
     <row r="28" ht="13.55" customHeight="1" s="24">
       <c r="A28" s="9" t="n">
@@ -3074,9 +2998,6 @@
       <c r="R28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S28" s="9" t="n">
-        <v>331</v>
-      </c>
     </row>
     <row r="29" ht="13.55" customHeight="1" s="24">
       <c r="A29" s="9" t="n">
@@ -3135,9 +3056,6 @@
       <c r="R29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S29" s="9" t="n">
-        <v>509</v>
-      </c>
     </row>
     <row r="30" ht="13.55" customHeight="1" s="24">
       <c r="A30" s="9" t="n">
@@ -3196,9 +3114,6 @@
       <c r="R30" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S30" s="9" t="n">
-        <v>683</v>
-      </c>
     </row>
     <row r="31" ht="13.55" customHeight="1" s="24">
       <c r="A31" s="9" t="n">
@@ -3257,9 +3172,6 @@
       <c r="R31" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S31" s="9" t="n">
-        <v>693</v>
-      </c>
     </row>
     <row r="32" ht="13.55" customHeight="1" s="24">
       <c r="A32" s="9" t="n">
@@ -3318,9 +3230,6 @@
       <c r="R32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S32" s="9" t="n">
-        <v>482</v>
-      </c>
     </row>
     <row r="33" ht="13.55" customHeight="1" s="24">
       <c r="A33" s="9" t="n">
@@ -3379,9 +3288,6 @@
       <c r="R33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S33" s="9" t="n">
-        <v>338</v>
-      </c>
     </row>
     <row r="34" ht="13.55" customHeight="1" s="24">
       <c r="A34" s="9" t="n">
@@ -3440,9 +3346,6 @@
       <c r="R34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S34" s="9" t="n">
-        <v>732</v>
-      </c>
     </row>
     <row r="35" ht="13.55" customHeight="1" s="24">
       <c r="A35" s="9" t="n">
@@ -3501,9 +3404,6 @@
       <c r="R35" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S35" s="9" t="n">
-        <v>723</v>
-      </c>
     </row>
     <row r="36" ht="13.55" customHeight="1" s="24">
       <c r="A36" s="9" t="n">
@@ -3562,9 +3462,6 @@
       <c r="R36" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S36" s="9" t="n">
-        <v>574</v>
-      </c>
     </row>
     <row r="37" ht="13.55" customHeight="1" s="24">
       <c r="A37" s="9" t="n">
@@ -3623,9 +3520,6 @@
       <c r="R37" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S37" s="9" t="n">
-        <v>319</v>
-      </c>
     </row>
     <row r="38" ht="13.55" customHeight="1" s="24">
       <c r="A38" s="9" t="n">
@@ -3684,9 +3578,6 @@
       <c r="R38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S38" s="9" t="n">
-        <v>597</v>
-      </c>
     </row>
     <row r="39" ht="13.55" customHeight="1" s="24">
       <c r="A39" s="9" t="n">
@@ -3745,9 +3636,6 @@
       <c r="R39" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S39" s="9" t="n">
-        <v>395</v>
-      </c>
     </row>
     <row r="40" ht="13.55" customHeight="1" s="24">
       <c r="A40" s="9" t="n">
@@ -3806,9 +3694,6 @@
       <c r="R40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S40" s="9" t="n">
-        <v>462</v>
-      </c>
     </row>
     <row r="41" ht="13.55" customHeight="1" s="24">
       <c r="A41" s="9" t="n">
@@ -3867,9 +3752,6 @@
       <c r="R41" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S41" s="9" t="n">
-        <v>547</v>
-      </c>
     </row>
     <row r="42" ht="13.55" customHeight="1" s="24">
       <c r="A42" s="9" t="n">
@@ -3928,9 +3810,6 @@
       <c r="R42" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S42" s="9" t="n">
-        <v>528</v>
-      </c>
     </row>
     <row r="43" ht="13.55" customHeight="1" s="24">
       <c r="A43" s="9" t="n">
@@ -3989,9 +3868,6 @@
       <c r="R43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S43" s="9" t="n">
-        <v>479</v>
-      </c>
     </row>
     <row r="44" ht="13.55" customHeight="1" s="24">
       <c r="A44" s="9" t="n">
@@ -4050,9 +3926,6 @@
       <c r="R44" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S44" s="9" t="n">
-        <v>772</v>
-      </c>
     </row>
     <row r="45" ht="26.55" customHeight="1" s="24">
       <c r="A45" s="9" t="n">
@@ -4112,9 +3985,6 @@
       <c r="R45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S45" s="9" t="n">
-        <v>520</v>
-      </c>
     </row>
     <row r="46" ht="13.55" customHeight="1" s="24">
       <c r="A46" s="9" t="n">
@@ -4173,9 +4043,6 @@
       <c r="R46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S46" s="9" t="n">
-        <v>517</v>
-      </c>
     </row>
     <row r="47" ht="13.55" customHeight="1" s="24">
       <c r="A47" s="9" t="n">
@@ -4234,9 +4101,6 @@
       <c r="R47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S47" s="9" t="n">
-        <v>897</v>
-      </c>
     </row>
     <row r="48" ht="13.55" customHeight="1" s="24">
       <c r="A48" s="9" t="n">
@@ -4295,9 +4159,6 @@
       <c r="R48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S48" s="9" t="n">
-        <v>470</v>
-      </c>
     </row>
     <row r="49" ht="13.55" customHeight="1" s="24">
       <c r="A49" s="9" t="n">
@@ -4356,9 +4217,6 @@
       <c r="R49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S49" s="9" t="n">
-        <v>417</v>
-      </c>
     </row>
     <row r="50" ht="13.55" customHeight="1" s="24">
       <c r="A50" s="9" t="n">
@@ -4417,9 +4275,6 @@
       <c r="R50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S50" s="9" t="n">
-        <v>606</v>
-      </c>
     </row>
     <row r="51" ht="13.55" customHeight="1" s="24">
       <c r="A51" s="9" t="n">
@@ -4478,9 +4333,6 @@
       <c r="R51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S51" s="9" t="n">
-        <v>615</v>
-      </c>
     </row>
     <row r="52" ht="13.55" customHeight="1" s="24">
       <c r="A52" s="9" t="n">
@@ -4539,9 +4391,6 @@
       <c r="R52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S52" s="9" t="n">
-        <v>557</v>
-      </c>
     </row>
     <row r="53" ht="13.55" customHeight="1" s="24">
       <c r="A53" s="9" t="n">
@@ -4600,9 +4449,6 @@
       <c r="R53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S53" s="9" t="n">
-        <v>759</v>
-      </c>
     </row>
     <row r="54" ht="13.55" customHeight="1" s="24">
       <c r="A54" s="9" t="n">
@@ -4661,9 +4507,6 @@
       <c r="R54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S54" s="9" t="n">
-        <v>717</v>
-      </c>
     </row>
     <row r="55" ht="13.55" customHeight="1" s="24">
       <c r="A55" s="9" t="n">
@@ -4722,9 +4565,6 @@
       <c r="R55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S55" s="9" t="n">
-        <v>511</v>
-      </c>
     </row>
     <row r="56" ht="13.55" customHeight="1" s="24">
       <c r="A56" s="9" t="n">
@@ -4783,9 +4623,6 @@
       <c r="R56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S56" s="9" t="n">
-        <v>531</v>
-      </c>
     </row>
     <row r="57" ht="13.55" customHeight="1" s="24">
       <c r="A57" s="9" t="n">
@@ -4844,9 +4681,6 @@
       <c r="R57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S57" s="9" t="n">
-        <v>600</v>
-      </c>
     </row>
     <row r="58" ht="13.55" customHeight="1" s="24">
       <c r="A58" s="9" t="n">
@@ -4905,9 +4739,6 @@
       <c r="R58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S58" s="9" t="n">
-        <v>489</v>
-      </c>
     </row>
     <row r="59" ht="13.55" customHeight="1" s="24">
       <c r="A59" s="9" t="n">
@@ -4966,9 +4797,6 @@
       <c r="R59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S59" s="9" t="n">
-        <v>663</v>
-      </c>
     </row>
     <row r="60" ht="13.55" customHeight="1" s="24">
       <c r="A60" s="9" t="n">
@@ -5027,9 +4855,6 @@
       <c r="R60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S60" s="9" t="n">
-        <v>622</v>
-      </c>
     </row>
     <row r="61" ht="13.55" customHeight="1" s="24">
       <c r="A61" s="9" t="n">
@@ -5088,9 +4913,6 @@
       <c r="R61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S61" s="9" t="n">
-        <v>548</v>
-      </c>
     </row>
     <row r="62" ht="13.55" customHeight="1" s="24">
       <c r="A62" s="9" t="n">
@@ -5149,9 +4971,6 @@
       <c r="R62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S62" s="9" t="n">
-        <v>802</v>
-      </c>
     </row>
     <row r="63" ht="13.55" customHeight="1" s="24">
       <c r="A63" s="9" t="n">
@@ -5210,9 +5029,6 @@
       <c r="R63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S63" s="9" t="n">
-        <v>455</v>
-      </c>
     </row>
     <row r="64" ht="13.55" customHeight="1" s="24">
       <c r="A64" s="9" t="n">
@@ -5271,9 +5087,6 @@
       <c r="R64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S64" s="9" t="n">
-        <v>371</v>
-      </c>
     </row>
     <row r="65" ht="13.55" customHeight="1" s="24">
       <c r="A65" s="9" t="n">
@@ -5332,9 +5145,6 @@
       <c r="R65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S65" s="9" t="n">
-        <v>447</v>
-      </c>
     </row>
     <row r="66" ht="13.55" customHeight="1" s="24">
       <c r="A66" s="9" t="n">
@@ -5393,9 +5203,6 @@
       <c r="R66" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S66" s="9" t="n">
-        <v>843</v>
-      </c>
     </row>
     <row r="67" ht="13.55" customHeight="1" s="24">
       <c r="A67" s="9" t="n">
@@ -5454,9 +5261,6 @@
       <c r="R67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S67" s="9" t="n">
-        <v>714</v>
-      </c>
     </row>
     <row r="68" ht="13.55" customHeight="1" s="24">
       <c r="A68" s="9" t="n">
@@ -5515,9 +5319,6 @@
       <c r="R68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S68" s="9" t="n">
-        <v>745</v>
-      </c>
     </row>
     <row r="69" ht="13.55" customHeight="1" s="24">
       <c r="A69" s="9" t="n">
@@ -5576,9 +5377,6 @@
       <c r="R69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S69" s="9" t="n">
-        <v>727</v>
-      </c>
     </row>
     <row r="70" ht="13.55" customHeight="1" s="24">
       <c r="A70" s="9" t="n">
@@ -5637,9 +5435,6 @@
       <c r="R70" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S70" s="9" t="n">
-        <v>610</v>
-      </c>
     </row>
     <row r="71" ht="13.55" customHeight="1" s="24">
       <c r="A71" s="9" t="n">
@@ -5698,9 +5493,6 @@
       <c r="R71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S71" s="9" t="n">
-        <v>874</v>
-      </c>
     </row>
     <row r="72" ht="13.55" customHeight="1" s="24">
       <c r="A72" s="9" t="n">
@@ -5759,9 +5551,6 @@
       <c r="R72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S72" s="9" t="n">
-        <v>360</v>
-      </c>
     </row>
     <row r="73" ht="13.55" customHeight="1" s="24">
       <c r="A73" s="9" t="n">
@@ -5820,9 +5609,6 @@
       <c r="R73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S73" s="9" t="n">
-        <v>494</v>
-      </c>
     </row>
     <row r="74" ht="13.55" customHeight="1" s="24">
       <c r="A74" s="9" t="n">
@@ -5881,9 +5667,6 @@
       <c r="R74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S74" s="9" t="n">
-        <v>529</v>
-      </c>
     </row>
     <row r="75" ht="13.55" customHeight="1" s="24">
       <c r="A75" s="9" t="n">
@@ -5942,9 +5725,6 @@
       <c r="R75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S75" s="9" t="n">
-        <v>272</v>
-      </c>
     </row>
     <row r="76" ht="13.55" customHeight="1" s="24">
       <c r="A76" s="9" t="n">
@@ -6003,9 +5783,6 @@
       <c r="R76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S76" s="9" t="n">
-        <v>942</v>
-      </c>
     </row>
     <row r="77" ht="13.55" customHeight="1" s="24">
       <c r="A77" s="9" t="n">
@@ -6064,9 +5841,6 @@
       <c r="R77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S77" s="9" t="n">
-        <v>862</v>
-      </c>
     </row>
     <row r="78" ht="13.55" customHeight="1" s="24">
       <c r="A78" s="9" t="n">
@@ -6125,9 +5899,6 @@
       <c r="R78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S78" s="9" t="n">
-        <v>534</v>
-      </c>
     </row>
     <row r="79" ht="13.55" customHeight="1" s="24">
       <c r="A79" s="9" t="n">
@@ -6186,9 +5957,6 @@
       <c r="R79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S79" s="9" t="n">
-        <v>349</v>
-      </c>
     </row>
     <row r="80" ht="13.55" customHeight="1" s="24">
       <c r="A80" s="9" t="n">
@@ -6247,9 +6015,6 @@
       <c r="R80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S80" s="9" t="n">
-        <v>646</v>
-      </c>
     </row>
     <row r="81" ht="13.55" customHeight="1" s="24">
       <c r="A81" s="9" t="n">
@@ -6308,9 +6073,6 @@
       <c r="R81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S81" s="9" t="n">
-        <v>636</v>
-      </c>
     </row>
     <row r="82" ht="13.55" customHeight="1" s="24">
       <c r="A82" s="9" t="n">
@@ -6369,9 +6131,6 @@
       <c r="R82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S82" s="9" t="n">
-        <v>532</v>
-      </c>
     </row>
     <row r="83" ht="13.55" customHeight="1" s="24">
       <c r="A83" s="9" t="n">
@@ -6430,9 +6189,6 @@
       <c r="R83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S83" s="9" t="n">
-        <v>751</v>
-      </c>
     </row>
     <row r="84" ht="13.55" customHeight="1" s="24">
       <c r="A84" s="9" t="n">
@@ -6491,9 +6247,6 @@
       <c r="R84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S84" s="9" t="n">
-        <v>556</v>
-      </c>
     </row>
     <row r="85" ht="13.55" customHeight="1" s="24">
       <c r="A85" s="9" t="n">
@@ -6552,9 +6305,6 @@
       <c r="R85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S85" s="9" t="n">
-        <v>556</v>
-      </c>
     </row>
     <row r="86" ht="13.55" customHeight="1" s="24">
       <c r="A86" s="9" t="n">
@@ -6613,9 +6363,6 @@
       <c r="R86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S86" s="9" t="n">
-        <v>482</v>
-      </c>
     </row>
     <row r="87" ht="13.55" customHeight="1" s="24">
       <c r="A87" s="9" t="n">
@@ -6674,9 +6421,6 @@
       <c r="R87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S87" s="9" t="n">
-        <v>448</v>
-      </c>
     </row>
     <row r="88" ht="13.55" customHeight="1" s="24">
       <c r="A88" s="9" t="n">
@@ -6735,9 +6479,6 @@
       <c r="R88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S88" s="9" t="n">
-        <v>857</v>
-      </c>
     </row>
     <row r="89" ht="13.55" customHeight="1" s="24">
       <c r="A89" s="9" t="n">
@@ -6796,9 +6537,6 @@
       <c r="R89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S89" s="9" t="n">
-        <v>572</v>
-      </c>
     </row>
     <row r="90" ht="13.55" customHeight="1" s="24">
       <c r="A90" s="9" t="n">
@@ -6857,9 +6595,6 @@
       <c r="R90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S90" s="9" t="n">
-        <v>637</v>
-      </c>
     </row>
     <row r="91" ht="13.55" customHeight="1" s="24">
       <c r="A91" s="9" t="n">
@@ -6918,9 +6653,6 @@
       <c r="R91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S91" s="9" t="n">
-        <v>336</v>
-      </c>
     </row>
     <row r="92" ht="13.55" customHeight="1" s="24">
       <c r="A92" s="9" t="n">
@@ -6979,9 +6711,6 @@
       <c r="R92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S92" s="9" t="n">
-        <v>424</v>
-      </c>
     </row>
     <row r="93" ht="13.55" customHeight="1" s="24">
       <c r="A93" s="9" t="n">
@@ -7040,9 +6769,6 @@
       <c r="R93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S93" s="9" t="n">
-        <v>409</v>
-      </c>
     </row>
     <row r="94" ht="13.55" customHeight="1" s="24">
       <c r="A94" s="9" t="n">
@@ -7101,9 +6827,6 @@
       <c r="R94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S94" s="9" t="n">
-        <v>691</v>
-      </c>
     </row>
     <row r="95" ht="26.55" customHeight="1" s="24">
       <c r="A95" s="9" t="n">
@@ -7163,9 +6886,6 @@
       <c r="R95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S95" s="9" t="n">
-        <v>446</v>
-      </c>
     </row>
     <row r="96" ht="13.55" customHeight="1" s="24">
       <c r="A96" s="9" t="n">
@@ -7224,9 +6944,6 @@
       <c r="R96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S96" s="9" t="n">
-        <v>459</v>
-      </c>
     </row>
     <row r="97" ht="13.55" customHeight="1" s="24">
       <c r="A97" s="9" t="n">
@@ -7285,9 +7002,6 @@
       <c r="R97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S97" s="9" t="n">
-        <v>740</v>
-      </c>
     </row>
     <row r="98" ht="13.55" customHeight="1" s="24">
       <c r="A98" s="9" t="n">
@@ -7346,9 +7060,6 @@
       <c r="R98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S98" s="9" t="n">
-        <v>718</v>
-      </c>
     </row>
     <row r="99" ht="13.55" customHeight="1" s="24">
       <c r="A99" s="9" t="n">
@@ -7407,9 +7118,6 @@
       <c r="R99" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S99" s="9" t="n">
-        <v>719</v>
-      </c>
     </row>
     <row r="100" ht="13.55" customHeight="1" s="24">
       <c r="A100" s="9" t="n">
@@ -7468,9 +7176,6 @@
       <c r="R100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S100" s="9" t="n">
-        <v>656</v>
-      </c>
     </row>
     <row r="101" ht="13.55" customHeight="1" s="24">
       <c r="A101" s="9" t="n">
@@ -7529,9 +7234,6 @@
       <c r="R101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S101" s="9" t="n">
-        <v>827</v>
-      </c>
     </row>
     <row r="102" ht="13.55" customHeight="1" s="24">
       <c r="A102" s="9" t="n">
@@ -7590,9 +7292,6 @@
       <c r="R102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S102" s="9" t="n">
-        <v>397</v>
-      </c>
     </row>
     <row r="103" ht="13.55" customHeight="1" s="24">
       <c r="A103" s="9" t="n">
@@ -7651,9 +7350,6 @@
       <c r="R103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S103" s="9" t="n">
-        <v>324</v>
-      </c>
     </row>
     <row r="104" ht="13.55" customHeight="1" s="24">
       <c r="A104" s="9" t="n">
@@ -7712,9 +7408,6 @@
       <c r="R104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S104" s="9" t="n">
-        <v>518</v>
-      </c>
     </row>
     <row r="105" ht="13.55" customHeight="1" s="24">
       <c r="A105" s="9" t="n">
@@ -7773,9 +7466,6 @@
       <c r="R105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S105" s="9" t="n">
-        <v>511</v>
-      </c>
     </row>
     <row r="106" ht="13.55" customHeight="1" s="24">
       <c r="A106" s="9" t="n">
@@ -7834,9 +7524,6 @@
       <c r="R106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S106" s="9" t="n">
-        <v>651</v>
-      </c>
     </row>
     <row r="107" ht="13.55" customHeight="1" s="24">
       <c r="A107" s="9" t="n">
@@ -7895,9 +7582,6 @@
       <c r="R107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S107" s="9" t="n">
-        <v>592</v>
-      </c>
     </row>
     <row r="108" ht="13.55" customHeight="1" s="24">
       <c r="A108" s="9" t="n">
@@ -7956,9 +7640,6 @@
       <c r="R108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S108" s="9" t="n">
-        <v>226</v>
-      </c>
     </row>
     <row r="109" ht="13.55" customHeight="1" s="24">
       <c r="A109" s="9" t="n">
@@ -8017,9 +7698,6 @@
       <c r="R109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S109" s="9" t="n">
-        <v>397</v>
-      </c>
     </row>
     <row r="110" ht="13.55" customHeight="1" s="24">
       <c r="A110" s="9" t="n">
@@ -8078,9 +7756,6 @@
       <c r="R110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S110" s="9" t="n">
-        <v>503</v>
-      </c>
     </row>
     <row r="111" ht="13.55" customHeight="1" s="24">
       <c r="A111" s="9" t="n">
@@ -8139,9 +7814,6 @@
       <c r="R111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S111" s="9" t="n">
-        <v>870</v>
-      </c>
     </row>
     <row r="112" ht="13.55" customHeight="1" s="24">
       <c r="A112" s="9" t="n">
@@ -8200,9 +7872,6 @@
       <c r="R112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S112" s="9" t="n">
-        <v>656</v>
-      </c>
     </row>
     <row r="113" ht="13.55" customHeight="1" s="24">
       <c r="A113" s="9" t="n">
@@ -8261,9 +7930,6 @@
       <c r="R113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S113" s="9" t="n">
-        <v>790</v>
-      </c>
     </row>
     <row r="114" ht="13.55" customHeight="1" s="24">
       <c r="A114" s="9" t="n">
@@ -8322,9 +7988,6 @@
       <c r="R114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S114" s="9" t="n">
-        <v>823</v>
-      </c>
     </row>
     <row r="115" ht="13.55" customHeight="1" s="24">
       <c r="A115" s="9" t="n">
@@ -8383,9 +8046,6 @@
       <c r="R115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S115" s="9" t="n">
-        <v>886</v>
-      </c>
     </row>
     <row r="116" ht="13.55" customHeight="1" s="24">
       <c r="A116" s="9" t="n">
@@ -8444,9 +8104,6 @@
       <c r="R116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S116" s="9" t="n">
-        <v>879</v>
-      </c>
     </row>
     <row r="117" ht="13.55" customHeight="1" s="24">
       <c r="A117" s="9" t="n">
@@ -8505,9 +8162,6 @@
       <c r="R117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S117" s="9" t="n">
-        <v>395</v>
-      </c>
     </row>
     <row r="118" ht="26.55" customHeight="1" s="24">
       <c r="A118" s="9" t="n">
@@ -8567,9 +8221,6 @@
       <c r="R118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S118" s="9" t="n">
-        <v>761</v>
-      </c>
     </row>
     <row r="119" ht="13.55" customHeight="1" s="24">
       <c r="A119" s="9" t="n">
@@ -8628,9 +8279,6 @@
       <c r="R119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S119" s="9" t="n">
-        <v>365</v>
-      </c>
     </row>
     <row r="120" ht="13.55" customHeight="1" s="24">
       <c r="A120" s="9" t="n">
@@ -8689,9 +8337,6 @@
       <c r="R120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S120" s="9" t="n">
-        <v>477</v>
-      </c>
     </row>
     <row r="121" ht="13.55" customHeight="1" s="24">
       <c r="A121" s="9" t="n">
@@ -8750,9 +8395,6 @@
       <c r="R121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S121" s="9" t="n">
-        <v>719</v>
-      </c>
     </row>
     <row r="122" ht="13.55" customHeight="1" s="24">
       <c r="A122" s="9" t="n">
@@ -8811,9 +8453,6 @@
       <c r="R122" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S122" s="9" t="n">
-        <v>685</v>
-      </c>
     </row>
     <row r="123" ht="13.55" customHeight="1" s="24">
       <c r="A123" s="9" t="n">
@@ -8872,9 +8511,6 @@
       <c r="R123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S123" s="9" t="n">
-        <v>847</v>
-      </c>
     </row>
     <row r="124" ht="13.55" customHeight="1" s="24">
       <c r="A124" s="9" t="n">
@@ -8933,9 +8569,6 @@
       <c r="R124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S124" s="9" t="n">
-        <v>543</v>
-      </c>
     </row>
     <row r="125" ht="13.55" customHeight="1" s="24">
       <c r="A125" s="9" t="n">
@@ -8994,9 +8627,6 @@
       <c r="R125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S125" s="9" t="n">
-        <v>699</v>
-      </c>
     </row>
     <row r="126" ht="13.55" customHeight="1" s="24">
       <c r="A126" s="9" t="n">
@@ -9055,9 +8685,6 @@
       <c r="R126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S126" s="9" t="n">
-        <v>809</v>
-      </c>
     </row>
     <row r="127" ht="13.55" customHeight="1" s="24">
       <c r="A127" s="9" t="n">
@@ -9116,9 +8743,6 @@
       <c r="R127" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S127" s="9" t="n">
-        <v>504</v>
-      </c>
     </row>
     <row r="128" ht="13.55" customHeight="1" s="24">
       <c r="A128" s="9" t="n">
@@ -9177,9 +8801,6 @@
       <c r="R128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S128" s="9" t="n">
-        <v>787</v>
-      </c>
     </row>
     <row r="129" ht="13.55" customHeight="1" s="24">
       <c r="A129" s="9" t="n">
@@ -9238,9 +8859,6 @@
       <c r="R129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S129" s="9" t="n">
-        <v>632</v>
-      </c>
     </row>
     <row r="130" ht="26.55" customHeight="1" s="24">
       <c r="A130" s="9" t="n">
@@ -9300,9 +8918,6 @@
       <c r="R130" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S130" s="9" t="n">
-        <v>360</v>
-      </c>
     </row>
     <row r="131" ht="13.55" customHeight="1" s="24">
       <c r="A131" s="9" t="n">
@@ -9361,9 +8976,6 @@
       <c r="R131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S131" s="9" t="n">
-        <v>656</v>
-      </c>
     </row>
     <row r="132" ht="26.55" customHeight="1" s="24">
       <c r="A132" s="9" t="n">
@@ -9423,9 +9035,6 @@
       <c r="R132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S132" s="9" t="n">
-        <v>217</v>
-      </c>
     </row>
     <row r="133" ht="13.55" customHeight="1" s="24">
       <c r="A133" s="9" t="n">
@@ -9484,9 +9093,6 @@
       <c r="R133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S133" s="9" t="n">
-        <v>318</v>
-      </c>
     </row>
     <row r="134" ht="13.55" customHeight="1" s="24">
       <c r="A134" s="9" t="n">
@@ -9545,9 +9151,6 @@
       <c r="R134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S134" s="9" t="n">
-        <v>605</v>
-      </c>
     </row>
     <row r="135" ht="13.55" customHeight="1" s="24">
       <c r="A135" s="9" t="n">
@@ -9606,9 +9209,6 @@
       <c r="R135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S135" s="9" t="n">
-        <v>606</v>
-      </c>
     </row>
     <row r="136" ht="13.55" customHeight="1" s="24">
       <c r="A136" s="9" t="n">
@@ -9667,9 +9267,6 @@
       <c r="R136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S136" s="9" t="n">
-        <v>664</v>
-      </c>
     </row>
     <row r="137" ht="13.55" customHeight="1" s="24">
       <c r="A137" s="9" t="n">
@@ -9728,9 +9325,6 @@
       <c r="R137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S137" s="9" t="n">
-        <v>823</v>
-      </c>
     </row>
     <row r="138" ht="13.55" customHeight="1" s="24">
       <c r="A138" s="9" t="n">
@@ -9789,9 +9383,6 @@
       <c r="R138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S138" s="9" t="n">
-        <v>325</v>
-      </c>
     </row>
     <row r="139" ht="13.55" customHeight="1" s="24">
       <c r="A139" s="9" t="n">
@@ -9850,9 +9441,6 @@
       <c r="R139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S139" s="9" t="n">
-        <v>515</v>
-      </c>
     </row>
     <row r="140" ht="13.55" customHeight="1" s="24">
       <c r="A140" s="9" t="n">
@@ -9911,9 +9499,6 @@
       <c r="R140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S140" s="9" t="n">
-        <v>742</v>
-      </c>
     </row>
     <row r="141" ht="13.55" customHeight="1" s="24">
       <c r="A141" s="9" t="n">
@@ -9972,9 +9557,6 @@
       <c r="R141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S141" s="9" t="n">
-        <v>427</v>
-      </c>
     </row>
     <row r="142" ht="13.55" customHeight="1" s="24">
       <c r="A142" s="9" t="n">
@@ -10033,9 +9615,6 @@
       <c r="R142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S142" s="9" t="n">
-        <v>276</v>
-      </c>
     </row>
     <row r="143" ht="13.55" customHeight="1" s="24">
       <c r="A143" s="9" t="n">
@@ -10094,9 +9673,6 @@
       <c r="R143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S143" s="9" t="n">
-        <v>778</v>
-      </c>
     </row>
     <row r="144" ht="13.55" customHeight="1" s="24">
       <c r="A144" s="9" t="n">
@@ -10155,9 +9731,6 @@
       <c r="R144" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S144" s="9" t="n">
-        <v>481</v>
-      </c>
     </row>
     <row r="145" ht="13.55" customHeight="1" s="24">
       <c r="A145" s="9" t="n">
@@ -10216,9 +9789,6 @@
       <c r="R145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S145" s="9" t="n">
-        <v>875</v>
-      </c>
     </row>
     <row r="146" ht="13.55" customHeight="1" s="24">
       <c r="A146" s="9" t="n">
@@ -10277,9 +9847,6 @@
       <c r="R146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S146" s="9" t="n">
-        <v>694</v>
-      </c>
     </row>
     <row r="147" ht="13.55" customHeight="1" s="24">
       <c r="A147" s="9" t="n">
@@ -10338,9 +9905,6 @@
       <c r="R147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S147" s="9" t="n">
-        <v>666</v>
-      </c>
     </row>
     <row r="148" ht="13.55" customHeight="1" s="24">
       <c r="A148" s="9" t="n">
@@ -10399,9 +9963,6 @@
       <c r="R148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S148" s="9" t="n">
-        <v>685</v>
-      </c>
     </row>
     <row r="149" ht="13.55" customHeight="1" s="24">
       <c r="A149" s="9" t="n">
@@ -10460,9 +10021,6 @@
       <c r="R149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S149" s="9" t="n">
-        <v>726</v>
-      </c>
     </row>
     <row r="150" ht="13.55" customHeight="1" s="24">
       <c r="A150" s="9" t="n">
@@ -10521,9 +10079,6 @@
       <c r="R150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S150" s="9" t="n">
-        <v>670</v>
-      </c>
     </row>
     <row r="151" ht="13.55" customHeight="1" s="24">
       <c r="A151" s="9" t="n">
@@ -10582,9 +10137,6 @@
       <c r="R151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S151" s="9" t="n">
-        <v>563</v>
-      </c>
     </row>
     <row r="152" ht="13.55" customHeight="1" s="24">
       <c r="A152" s="9" t="n">
@@ -10643,9 +10195,6 @@
       <c r="R152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S152" s="9" t="n">
-        <v>500</v>
-      </c>
     </row>
     <row r="153" ht="13.55" customHeight="1" s="24">
       <c r="A153" s="9" t="n">
@@ -10704,9 +10253,6 @@
       <c r="R153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S153" s="9" t="n">
-        <v>437</v>
-      </c>
     </row>
     <row r="154" ht="13.55" customHeight="1" s="24">
       <c r="A154" s="9" t="n">
@@ -10765,9 +10311,6 @@
       <c r="R154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S154" s="9" t="n">
-        <v>483</v>
-      </c>
     </row>
     <row r="155" ht="13.55" customHeight="1" s="24">
       <c r="A155" s="9" t="n">
@@ -10826,9 +10369,6 @@
       <c r="R155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S155" s="9" t="n">
-        <v>718</v>
-      </c>
     </row>
     <row r="156" ht="13.55" customHeight="1" s="24">
       <c r="A156" s="9" t="n">
@@ -10887,9 +10427,6 @@
       <c r="R156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S156" s="9" t="n">
-        <v>590</v>
-      </c>
     </row>
     <row r="157" ht="26.55" customHeight="1" s="24">
       <c r="A157" s="9" t="n">
@@ -10949,9 +10486,6 @@
       <c r="R157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S157" s="9" t="n">
-        <v>427</v>
-      </c>
     </row>
     <row r="158" ht="13.55" customHeight="1" s="24">
       <c r="A158" s="9" t="n">
@@ -11010,9 +10544,6 @@
       <c r="R158" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S158" s="9" t="n">
-        <v>565</v>
-      </c>
     </row>
     <row r="159" ht="13.55" customHeight="1" s="24">
       <c r="A159" s="9" t="n">
@@ -11071,9 +10602,6 @@
       <c r="R159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S159" s="9" t="n">
-        <v>650</v>
-      </c>
     </row>
     <row r="160" ht="13.55" customHeight="1" s="24">
       <c r="A160" s="9" t="n">
@@ -11132,9 +10660,6 @@
       <c r="R160" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S160" s="9" t="n">
-        <v>359</v>
-      </c>
     </row>
     <row r="161" ht="13.55" customHeight="1" s="24">
       <c r="A161" s="9" t="n">
@@ -11193,9 +10718,6 @@
       <c r="R161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S161" s="9" t="n">
-        <v>472</v>
-      </c>
     </row>
     <row r="162" ht="13.55" customHeight="1" s="24">
       <c r="A162" s="9" t="n">
@@ -11254,9 +10776,6 @@
       <c r="R162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S162" s="9" t="n">
-        <v>546</v>
-      </c>
     </row>
     <row r="163" ht="13.55" customHeight="1" s="24">
       <c r="A163" s="9" t="n">
@@ -11315,9 +10834,6 @@
       <c r="R163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S163" s="9" t="n">
-        <v>262</v>
-      </c>
     </row>
     <row r="164" ht="13.55" customHeight="1" s="24">
       <c r="A164" s="9" t="n">
@@ -11376,9 +10892,6 @@
       <c r="R164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S164" s="9" t="n">
-        <v>573</v>
-      </c>
     </row>
     <row r="165" ht="13.55" customHeight="1" s="24">
       <c r="A165" s="9" t="n">
@@ -11437,9 +10950,6 @@
       <c r="R165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S165" s="9" t="n">
-        <v>266</v>
-      </c>
     </row>
     <row r="166" ht="13.55" customHeight="1" s="24">
       <c r="A166" s="9" t="n">
@@ -11498,9 +11008,6 @@
       <c r="R166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S166" s="9" t="n">
-        <v>726</v>
-      </c>
     </row>
     <row r="167" ht="13.55" customHeight="1" s="24">
       <c r="A167" s="9" t="n">
@@ -11559,9 +11066,6 @@
       <c r="R167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S167" s="9" t="n">
-        <v>682</v>
-      </c>
     </row>
     <row r="168" ht="13.55" customHeight="1" s="24">
       <c r="A168" s="9" t="n">
@@ -11620,9 +11124,6 @@
       <c r="R168" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S168" s="9" t="n">
-        <v>816</v>
-      </c>
     </row>
     <row r="169" ht="13.55" customHeight="1" s="24">
       <c r="A169" s="9" t="n">
@@ -11681,9 +11182,6 @@
       <c r="R169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S169" s="9" t="n">
-        <v>875</v>
-      </c>
     </row>
     <row r="170" ht="13.55" customHeight="1" s="24">
       <c r="A170" s="9" t="n">
@@ -11742,9 +11240,6 @@
       <c r="R170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S170" s="9" t="n">
-        <v>503</v>
-      </c>
     </row>
     <row r="171" ht="13.55" customHeight="1" s="24">
       <c r="A171" s="9" t="n">
@@ -11803,9 +11298,6 @@
       <c r="R171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S171" s="9" t="n">
-        <v>529</v>
-      </c>
     </row>
     <row r="172" ht="13.55" customHeight="1" s="24">
       <c r="A172" s="9" t="n">
@@ -11864,9 +11356,6 @@
       <c r="R172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S172" s="9" t="n">
-        <v>924</v>
-      </c>
     </row>
     <row r="173" ht="13.55" customHeight="1" s="24">
       <c r="A173" s="9" t="n">
@@ -11925,9 +11414,6 @@
       <c r="R173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S173" s="9" t="n">
-        <v>545</v>
-      </c>
     </row>
     <row r="174" ht="13.55" customHeight="1" s="24">
       <c r="A174" s="9" t="n">
@@ -11986,9 +11472,6 @@
       <c r="R174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S174" s="9" t="n">
-        <v>879</v>
-      </c>
     </row>
     <row r="175" ht="13.55" customHeight="1" s="24">
       <c r="A175" s="9" t="n">
@@ -12047,9 +11530,6 @@
       <c r="R175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S175" s="9" t="n">
-        <v>583</v>
-      </c>
     </row>
     <row r="176" ht="13.55" customHeight="1" s="24">
       <c r="A176" s="9" t="n">
@@ -12108,9 +11588,6 @@
       <c r="R176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S176" s="9" t="n">
-        <v>688</v>
-      </c>
     </row>
     <row r="177" ht="13.55" customHeight="1" s="24">
       <c r="A177" s="9" t="n">
@@ -12169,9 +11646,6 @@
       <c r="R177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S177" s="9" t="n">
-        <v>567</v>
-      </c>
     </row>
     <row r="178" ht="13.55" customHeight="1" s="24">
       <c r="A178" s="9" t="n">
@@ -12230,9 +11704,6 @@
       <c r="R178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S178" s="9" t="n">
-        <v>413</v>
-      </c>
     </row>
     <row r="179" ht="13.55" customHeight="1" s="24">
       <c r="A179" s="9" t="n">
@@ -12291,9 +11762,6 @@
       <c r="R179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S179" s="9" t="n">
-        <v>693</v>
-      </c>
     </row>
     <row r="180" ht="13.55" customHeight="1" s="24">
       <c r="A180" s="9" t="n">
@@ -12352,9 +11820,6 @@
       <c r="R180" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S180" s="9" t="n">
-        <v>458</v>
-      </c>
     </row>
     <row r="181" ht="13.55" customHeight="1" s="24">
       <c r="A181" s="9" t="n">
@@ -12413,9 +11878,6 @@
       <c r="R181" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S181" s="9" t="n">
-        <v>533</v>
-      </c>
     </row>
     <row r="182" ht="13.55" customHeight="1" s="24">
       <c r="A182" s="9" t="n">
@@ -12474,9 +11936,6 @@
       <c r="R182" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S182" s="9" t="n">
-        <v>919</v>
-      </c>
     </row>
     <row r="183" ht="13.55" customHeight="1" s="24">
       <c r="A183" s="9" t="n">
@@ -12535,9 +11994,6 @@
       <c r="R183" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S183" s="9" t="n">
-        <v>394</v>
-      </c>
     </row>
     <row r="184" ht="13.55" customHeight="1" s="24">
       <c r="A184" s="9" t="n">
@@ -12596,9 +12052,6 @@
       <c r="R184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S184" s="9" t="n">
-        <v>402</v>
-      </c>
     </row>
     <row r="185" ht="13.55" customHeight="1" s="24">
       <c r="A185" s="9" t="n">
@@ -12657,9 +12110,6 @@
       <c r="R185" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S185" s="9" t="n">
-        <v>729</v>
-      </c>
     </row>
     <row r="186" ht="13.55" customHeight="1" s="24">
       <c r="A186" s="9" t="n">
@@ -12718,9 +12168,6 @@
       <c r="R186" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S186" s="9" t="n">
-        <v>411</v>
-      </c>
     </row>
     <row r="187" ht="13.55" customHeight="1" s="24">
       <c r="A187" s="9" t="n">
@@ -12779,9 +12226,6 @@
       <c r="R187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S187" s="9" t="n">
-        <v>285</v>
-      </c>
     </row>
     <row r="188" ht="13.55" customHeight="1" s="24">
       <c r="A188" s="9" t="n">
@@ -12840,9 +12284,6 @@
       <c r="R188" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S188" s="9" t="n">
-        <v>660</v>
-      </c>
     </row>
     <row r="189" ht="13.55" customHeight="1" s="24">
       <c r="A189" s="9" t="n">
@@ -12901,9 +12342,6 @@
       <c r="R189" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S189" s="9" t="n">
-        <v>569</v>
-      </c>
     </row>
     <row r="190" ht="13.55" customHeight="1" s="24">
       <c r="A190" s="9" t="n">
@@ -12962,9 +12400,6 @@
       <c r="R190" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S190" s="9" t="n">
-        <v>590</v>
-      </c>
     </row>
     <row r="191" ht="13.55" customHeight="1" s="24">
       <c r="A191" s="9" t="n">
@@ -13023,9 +12458,6 @@
       <c r="R191" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S191" s="9" t="n">
-        <v>363</v>
-      </c>
     </row>
     <row r="192" ht="13.55" customHeight="1" s="24">
       <c r="A192" s="9" t="n">
@@ -13084,9 +12516,6 @@
       <c r="R192" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S192" s="9" t="n">
-        <v>478</v>
-      </c>
     </row>
     <row r="193" ht="13.55" customHeight="1" s="24">
       <c r="A193" s="9" t="n">
@@ -13145,9 +12574,6 @@
       <c r="R193" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S193" s="9" t="n">
-        <v>446</v>
-      </c>
     </row>
     <row r="194" ht="13.55" customHeight="1" s="24">
       <c r="A194" s="9" t="n">
@@ -13206,9 +12632,6 @@
       <c r="R194" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S194" s="9" t="n">
-        <v>485</v>
-      </c>
     </row>
     <row r="195" ht="13.55" customHeight="1" s="24">
       <c r="A195" s="9" t="n">
@@ -13267,9 +12690,6 @@
       <c r="R195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S195" s="9" t="n">
-        <v>705</v>
-      </c>
     </row>
     <row r="196" ht="13.55" customHeight="1" s="24">
       <c r="A196" s="9" t="n">
@@ -13328,9 +12748,6 @@
       <c r="R196" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S196" s="9" t="n">
-        <v>322</v>
-      </c>
     </row>
     <row r="197" ht="13.55" customHeight="1" s="24">
       <c r="A197" s="9" t="n">
@@ -13389,9 +12806,6 @@
       <c r="R197" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S197" s="9" t="n">
-        <v>806</v>
-      </c>
     </row>
     <row r="198" ht="13.55" customHeight="1" s="24">
       <c r="A198" s="9" t="n">
@@ -13450,9 +12864,6 @@
       <c r="R198" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S198" s="9" t="n">
-        <v>568</v>
-      </c>
     </row>
     <row r="199" ht="13.55" customHeight="1" s="24">
       <c r="A199" s="9" t="n">
@@ -13511,9 +12922,6 @@
       <c r="R199" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S199" s="9" t="n">
-        <v>553</v>
-      </c>
     </row>
     <row r="200" ht="13.55" customHeight="1" s="24">
       <c r="A200" s="9" t="n">
@@ -13572,9 +12980,6 @@
       <c r="R200" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S200" s="9" t="n">
-        <v>467</v>
-      </c>
     </row>
     <row r="201" ht="13.55" customHeight="1" s="24">
       <c r="A201" s="9" t="n">
@@ -13633,9 +13038,6 @@
       <c r="R201" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S201" s="9" t="n">
-        <v>466</v>
-      </c>
     </row>
     <row r="202" ht="13.55" customHeight="1" s="24">
       <c r="A202" s="9" t="n">
@@ -13694,9 +13096,6 @@
       <c r="R202" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S202" s="9" t="n">
-        <v>556</v>
-      </c>
     </row>
     <row r="203" ht="13.55" customHeight="1" s="24">
       <c r="A203" s="9" t="n">
@@ -13755,9 +13154,6 @@
       <c r="R203" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S203" s="9" t="n">
-        <v>657</v>
-      </c>
     </row>
     <row r="204" ht="13.55" customHeight="1" s="24">
       <c r="A204" s="9" t="n">
@@ -13816,9 +13212,6 @@
       <c r="R204" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S204" s="9" t="n">
-        <v>384</v>
-      </c>
     </row>
     <row r="205" ht="13.55" customHeight="1" s="24">
       <c r="A205" s="9" t="n">
@@ -13877,9 +13270,6 @@
       <c r="R205" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S205" s="9" t="n">
-        <v>649</v>
-      </c>
     </row>
     <row r="206" ht="13.55" customHeight="1" s="24">
       <c r="A206" s="9" t="n">
@@ -13938,9 +13328,6 @@
       <c r="R206" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S206" s="9" t="n">
-        <v>689</v>
-      </c>
     </row>
     <row r="207" ht="13.55" customHeight="1" s="24">
       <c r="A207" s="9" t="n">
@@ -13999,9 +13386,6 @@
       <c r="R207" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S207" s="9" t="n">
-        <v>768</v>
-      </c>
     </row>
     <row r="208" ht="13.55" customHeight="1" s="24">
       <c r="A208" s="9" t="n">
@@ -14060,9 +13444,6 @@
       <c r="R208" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S208" s="9" t="n">
-        <v>646</v>
-      </c>
     </row>
     <row r="209" ht="13.55" customHeight="1" s="24">
       <c r="A209" s="9" t="n">
@@ -14121,9 +13502,6 @@
       <c r="R209" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S209" s="9" t="n">
-        <v>675</v>
-      </c>
     </row>
     <row r="210" ht="26.55" customHeight="1" s="24">
       <c r="A210" s="9" t="n">
@@ -14183,9 +13561,6 @@
       <c r="R210" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S210" s="9" t="n">
-        <v>440</v>
-      </c>
     </row>
     <row r="211" ht="13.55" customHeight="1" s="24">
       <c r="A211" s="9" t="n">
@@ -14244,9 +13619,6 @@
       <c r="R211" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S211" s="9" t="n">
-        <v>542</v>
-      </c>
     </row>
     <row r="212" ht="13.55" customHeight="1" s="24">
       <c r="A212" s="9" t="n">
@@ -14305,9 +13677,6 @@
       <c r="R212" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S212" s="9" t="n">
-        <v>623</v>
-      </c>
     </row>
     <row r="213" ht="13.55" customHeight="1" s="24">
       <c r="A213" s="9" t="n">
@@ -14366,9 +13735,6 @@
       <c r="R213" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S213" s="9" t="n">
-        <v>526</v>
-      </c>
     </row>
     <row r="214" ht="13.55" customHeight="1" s="24">
       <c r="A214" s="9" t="n">
@@ -14427,9 +13793,6 @@
       <c r="R214" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S214" s="9" t="n">
-        <v>480</v>
-      </c>
     </row>
     <row r="215" ht="13.55" customHeight="1" s="24">
       <c r="A215" s="9" t="n">
@@ -14488,9 +13851,6 @@
       <c r="R215" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S215" s="9" t="n">
-        <v>669</v>
-      </c>
     </row>
     <row r="216" ht="13.55" customHeight="1" s="24">
       <c r="A216" s="9" t="n">
@@ -14549,9 +13909,6 @@
       <c r="R216" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S216" s="9" t="n">
-        <v>703</v>
-      </c>
     </row>
     <row r="217" ht="13.55" customHeight="1" s="24">
       <c r="A217" s="9" t="n">
@@ -14610,9 +13967,6 @@
       <c r="R217" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S217" s="9" t="n">
-        <v>633</v>
-      </c>
     </row>
     <row r="218" ht="13.55" customHeight="1" s="24">
       <c r="A218" s="9" t="n">
@@ -14671,9 +14025,6 @@
       <c r="R218" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S218" s="9" t="n">
-        <v>434</v>
-      </c>
     </row>
     <row r="219" ht="13.55" customHeight="1" s="24">
       <c r="A219" s="9" t="n">
@@ -14732,9 +14083,6 @@
       <c r="R219" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S219" s="9" t="n">
-        <v>480</v>
-      </c>
     </row>
     <row r="220" ht="13.55" customHeight="1" s="24">
       <c r="A220" s="9" t="n">
@@ -14793,9 +14141,6 @@
       <c r="R220" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S220" s="9" t="n">
-        <v>451</v>
-      </c>
     </row>
     <row r="221" ht="13.55" customHeight="1" s="24">
       <c r="A221" s="9" t="n">
@@ -14854,9 +14199,6 @@
       <c r="R221" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S221" s="9" t="n">
-        <v>468</v>
-      </c>
     </row>
     <row r="222" ht="13.55" customHeight="1" s="24">
       <c r="A222" s="9" t="n">
@@ -14915,9 +14257,6 @@
       <c r="R222" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S222" s="9" t="n">
-        <v>471</v>
-      </c>
     </row>
     <row r="223" ht="13.55" customHeight="1" s="24">
       <c r="A223" s="9" t="n">
@@ -14976,9 +14315,6 @@
       <c r="R223" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S223" s="9" t="n">
-        <v>586</v>
-      </c>
     </row>
     <row r="224" ht="13.55" customHeight="1" s="24">
       <c r="A224" s="9" t="n">
@@ -15037,9 +14373,6 @@
       <c r="R224" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S224" s="9" t="n">
-        <v>833</v>
-      </c>
     </row>
     <row r="225" ht="13.55" customHeight="1" s="24">
       <c r="A225" s="9" t="n">
@@ -15098,9 +14431,6 @@
       <c r="R225" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S225" s="9" t="n">
-        <v>908</v>
-      </c>
     </row>
     <row r="226" ht="13.55" customHeight="1" s="24">
       <c r="A226" s="9" t="n">
@@ -15159,9 +14489,6 @@
       <c r="R226" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S226" s="9" t="n">
-        <v>460</v>
-      </c>
     </row>
     <row r="227" ht="13.55" customHeight="1" s="24">
       <c r="A227" s="9" t="n">
@@ -15220,9 +14547,6 @@
       <c r="R227" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S227" s="9" t="n">
-        <v>436</v>
-      </c>
     </row>
     <row r="228" ht="13.55" customHeight="1" s="24">
       <c r="A228" s="9" t="n">
@@ -15281,9 +14605,6 @@
       <c r="R228" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S228" s="9" t="n">
-        <v>678</v>
-      </c>
     </row>
     <row r="229" ht="13.55" customHeight="1" s="24">
       <c r="A229" s="9" t="n">
@@ -15342,9 +14663,6 @@
       <c r="R229" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S229" s="9" t="n">
-        <v>445</v>
-      </c>
     </row>
     <row r="230" ht="13.55" customHeight="1" s="24">
       <c r="A230" s="9" t="n">
@@ -15403,9 +14721,6 @@
       <c r="R230" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S230" s="9" t="n">
-        <v>329</v>
-      </c>
     </row>
     <row r="231" ht="13.55" customHeight="1" s="24">
       <c r="A231" s="9" t="n">
@@ -15464,9 +14779,6 @@
       <c r="R231" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S231" s="9" t="n">
-        <v>778</v>
-      </c>
     </row>
     <row r="232" ht="13.55" customHeight="1" s="24">
       <c r="A232" s="9" t="n">
@@ -15525,9 +14837,6 @@
       <c r="R232" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S232" s="9" t="n">
-        <v>563</v>
-      </c>
     </row>
     <row r="233" ht="13.55" customHeight="1" s="24">
       <c r="A233" s="9" t="n">
@@ -15586,9 +14895,6 @@
       <c r="R233" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S233" s="9" t="n">
-        <v>517</v>
-      </c>
     </row>
     <row r="234" ht="13.55" customHeight="1" s="24">
       <c r="A234" s="9" t="n">
@@ -15647,9 +14953,6 @@
       <c r="R234" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S234" s="9" t="n">
-        <v>540</v>
-      </c>
     </row>
     <row r="235" ht="13.55" customHeight="1" s="24">
       <c r="A235" s="9" t="n">
@@ -15708,9 +15011,6 @@
       <c r="R235" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S235" s="9" t="n">
-        <v>610</v>
-      </c>
     </row>
     <row r="236" ht="13.55" customHeight="1" s="24">
       <c r="A236" s="9" t="n">
@@ -15769,9 +15069,6 @@
       <c r="R236" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S236" s="9" t="n">
-        <v>683</v>
-      </c>
     </row>
     <row r="237" ht="13.55" customHeight="1" s="24">
       <c r="A237" s="9" t="n">
@@ -15830,9 +15127,6 @@
       <c r="R237" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S237" s="9" t="n">
-        <v>338</v>
-      </c>
     </row>
     <row r="238" ht="13.55" customHeight="1" s="24">
       <c r="A238" s="9" t="n">
@@ -15891,9 +15185,6 @@
       <c r="R238" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S238" s="9" t="n">
-        <v>513</v>
-      </c>
     </row>
     <row r="239" ht="13.55" customHeight="1" s="24">
       <c r="A239" s="9" t="n">
@@ -15952,9 +15243,6 @@
       <c r="R239" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S239" s="9" t="n">
-        <v>701</v>
-      </c>
     </row>
     <row r="240" ht="13.55" customHeight="1" s="24">
       <c r="A240" s="9" t="n">
@@ -16013,9 +15301,6 @@
       <c r="R240" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S240" s="9" t="n">
-        <v>225</v>
-      </c>
     </row>
     <row r="241" ht="13.55" customHeight="1" s="24">
       <c r="A241" s="9" t="n">
@@ -16074,9 +15359,6 @@
       <c r="R241" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S241" s="9" t="n">
-        <v>278</v>
-      </c>
     </row>
     <row r="242" ht="13.55" customHeight="1" s="24">
       <c r="A242" s="9" t="n">
@@ -16135,9 +15417,6 @@
       <c r="R242" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S242" s="9" t="n">
-        <v>487</v>
-      </c>
     </row>
     <row r="243" ht="13.55" customHeight="1" s="24">
       <c r="A243" s="9" t="n">
@@ -16196,9 +15475,6 @@
       <c r="R243" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S243" s="9" t="n">
-        <v>692</v>
-      </c>
     </row>
     <row r="244" ht="26.55" customHeight="1" s="24">
       <c r="A244" s="9" t="n">
@@ -16258,9 +15534,6 @@
       <c r="R244" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S244" s="9" t="n">
-        <v>285</v>
-      </c>
     </row>
     <row r="245" ht="26.55" customHeight="1" s="24">
       <c r="A245" s="9" t="n">
@@ -16320,9 +15593,6 @@
       <c r="R245" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S245" s="9" t="n">
-        <v>578</v>
-      </c>
     </row>
     <row r="246" ht="26.55" customHeight="1" s="24">
       <c r="A246" s="9" t="n">
@@ -16382,9 +15652,6 @@
       <c r="R246" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S246" s="9" t="n">
-        <v>727</v>
-      </c>
     </row>
     <row r="247" ht="13.55" customHeight="1" s="24">
       <c r="A247" s="9" t="n">
@@ -16443,9 +15710,6 @@
       <c r="R247" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S247" s="9" t="n">
-        <v>684</v>
-      </c>
     </row>
     <row r="248" ht="14.05" customHeight="1" s="24">
       <c r="A248" s="12" t="n">
@@ -16504,9 +15768,6 @@
       <c r="R248" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S248" s="9" t="n">
-        <v>657</v>
-      </c>
     </row>
     <row r="249" ht="14.15" customHeight="1" s="24">
       <c r="A249" s="14" t="inlineStr">
@@ -16563,9 +15824,6 @@
       <c r="R249" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="S249" s="16" t="n">
-        <v>140493</v>
-      </c>
     </row>
     <row r="250" ht="13.65" customHeight="1" s="24">
       <c r="A250" s="17" t="inlineStr">
@@ -16622,9 +15880,6 @@
       <c r="R250" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="S250" s="16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="251" ht="13.65" customHeight="1" s="24">
       <c r="A251" s="19" t="inlineStr">
@@ -16678,11 +15933,8 @@
       <c r="Q251" s="22" t="n">
         <v>141204</v>
       </c>
-      <c r="R251" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S251" s="23" t="n">
-        <v>140493</v>
+      <c r="R251" s="23" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
